--- a/samples/ss_ungaran12_ingest.xlsx
+++ b/samples/ss_ungaran12_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,31 +806,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -879,31 +849,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -932,31 +892,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -985,31 +935,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1038,19 +978,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1066,7 +998,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1095,19 +1026,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1123,7 +1046,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1152,31 +1074,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1205,19 +1117,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1233,7 +1137,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1262,19 +1165,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1290,7 +1185,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1319,19 +1213,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1347,7 +1233,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1376,31 +1261,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1429,19 +1304,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1457,7 +1324,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1486,19 +1352,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1514,7 +1372,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1543,23 +1400,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>KTT APF</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1575,7 +1425,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1604,31 +1453,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1657,19 +1496,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1685,7 +1516,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1714,19 +1544,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1742,7 +1564,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1771,19 +1592,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1799,7 +1612,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1828,17 +1640,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1854,13 +1660,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1889,17 +1693,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1915,13 +1713,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1950,17 +1746,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1976,13 +1766,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2011,17 +1799,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2037,13 +1819,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2072,17 +1852,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2098,13 +1872,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2211,7 +1983,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTA Jelok</t>
@@ -2232,7 +2003,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2246,8 +2016,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2264,13 +2032,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Timo</t>
@@ -2291,7 +2057,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -2305,8 +2070,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2323,13 +2086,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTGU Tambaklorok Blok B3</t>
@@ -2350,7 +2111,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -2364,8 +2124,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2382,13 +2140,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Outlet PLTGU Tambaklorok Blok B1</t>
@@ -2409,7 +2165,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -2423,8 +2178,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2441,13 +2194,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Jelok - Ungaran</t>
@@ -2468,7 +2219,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2482,8 +2232,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2500,7 +2248,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2531,7 +2278,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -2545,8 +2291,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2563,13 +2307,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Jelok - Banaran (arah SS Boyolali)</t>
@@ -2590,7 +2332,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2604,8 +2345,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2622,7 +2361,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2653,7 +2391,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2667,8 +2404,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2685,7 +2420,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2716,7 +2450,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2730,8 +2463,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2748,7 +2479,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2779,7 +2509,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2793,8 +2522,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2811,13 +2538,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Tambaklorok - Pandean Lamper</t>
@@ -2838,7 +2563,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2852,8 +2576,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2870,7 +2592,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2901,7 +2622,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2915,8 +2635,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2933,7 +2651,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2964,7 +2681,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -2978,8 +2694,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2996,7 +2710,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3027,7 +2740,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3041,8 +2753,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3059,7 +2769,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3090,7 +2799,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3104,8 +2812,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3122,13 +2828,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Weleri - New Batang (arah SS Pemalang)</t>
@@ -3149,7 +2853,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3163,8 +2866,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3181,13 +2882,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Weleri - Bumi Putih (arah SS Pemalang)</t>
@@ -3208,7 +2907,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3222,8 +2920,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3240,13 +2936,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Payung - Bawen Sambiroto Baru</t>
@@ -3267,7 +2961,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3281,8 +2974,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3299,7 +2990,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3330,7 +3020,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3344,8 +3033,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3362,13 +3049,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT Pandean Lamper - Srondol</t>
@@ -3389,7 +3074,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -3403,8 +3087,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3421,7 +3103,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3452,7 +3133,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -3466,8 +3146,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3484,13 +3162,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Sayung - Tanjung Jati (arah SS Tanjung Jati)</t>
@@ -3511,7 +3187,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -3525,8 +3200,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3543,13 +3216,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Sayung - Kudus (arah SS Tanjung Jati)</t>
@@ -3570,7 +3241,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -3584,8 +3254,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3602,7 +3270,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3671,22 +3338,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1, 2 GITET Ungaran &gt;60% sehingga N-1 tidak terpenuhisaatPLTGU Tambaklorok tidak beroperasi</t>
+          <t>[N-1] Pembebanan IBT 1, 2 GITET Ungaran &gt;60% sehingga N-1 tidak terpenuhi saat PLTGU Tambaklorok tidak beroperasi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.TerjadiOverloadsaat gangguan salah satu IBT (N-1-1). 2.Berpotensi padam beban sebesar 528 MW saat kondisi N- 1-1. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. TerjadiOverloadsaat gangguan salah satu IBT (N-1-1). 2. Berpotensi padam beban sebesar 528 MW saat kondisi N- 1-1. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2 Ungaran total target sebesar 528 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 -5.721 MW). 3.Sudah terpasang skema proteksi island Subsistem Ungaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran (kombinasi) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
+          <t>1. Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2. Sudah terpasang OLS IBT 1,2 Ungaran total target sebesar 528 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3. Sudah terpasang skema proteksi island Subsistem Ungaran 1,2. 4. Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran (kombinasi) 5. Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD tahun 2028. (menunggu kepastian dari KEK Kendal) Jangka Panjang: 2.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD tahun 2032</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD tahun 2028. (menunggu kepastian dari KEK Kendal) Jangka Panjang : 2. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD tahun 2032</t>
         </is>
       </c>
     </row>
@@ -3706,22 +3373,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1, 2 dan 3 GITET Ungaran &gt;60% saat dioperasikan looping 3 IBT sehingga N-1 tidak terpenuhisaatPLTGU Tambaklorok tidak beroperasi</t>
+          <t>[N-1] Pembebanan IBT 1, 2 dan 3 GITET Ungaran &gt;60% saat dioperasikan looping 3 IBT sehingga N-1 tidak terpenuhi saat PLTGU Tambaklorok tidak beroperasi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT (N-1-1). 2.Berpotensi padam beban sebesar 528 MW saat kondisi N- 1-1. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT (N-1-1). 2. Berpotensi padam beban sebesar 528 MW saat kondisi N- 1-1. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Sudah terpasang OLS IBT 1,2,3 Ungaran (Looping) total target sebesar 541MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3.Sudah terpasang skema proteksi island SubsistemUngaran 1,2. 4.Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran(kombinasi) 5.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
+          <t>1. Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2. Sudah terpasang OLS IBT 1,2,3 Ungaran (Looping) total target sebesar 541 MW(Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 3. Sudah terpasang skema proteksi island Subsistem Ungaran 1,2. 4. Pelaksanaan pemeliharaan saat beban rendah/hari libur, looping dengan IBT 3 Ungaran &amp; sudah terpasang OLS IBT 1,2,3 Ungaran (kombinasi) 5. Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD tahun 2028. (menunggu kepastian dari KEK Kendal) JangkaPanjang: 2.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD tahun 2032</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD tahun 2028. (menunggu kepastian dari KEK Kendal) Jangka Panjang: 2. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD tahun 2032</t>
         </is>
       </c>
     </row>
@@ -3746,17 +3413,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Keandalan Unit PLTGU Tambaklorok blok 1 berkurang. 2.Dapat menyebabkan kerusakan peralatan jika SCL terlalu besar</t>
+          <t>1. Keandalan Unit PLTGU Tambaklorok blok 1 berkurang. 2. Dapat menyebabkan kerusakan peralatan jika SCL terlalu besar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Busbar PLTGU Blok 2 Tambaklorok dioperasikan Splitting dan beda Subsistem. 2.Pengoperasian PLTGU Tambaklorok dioperasikan maksimal 5 unit dalam Subsistem Ungaran 1,2</t>
+          <t>1. Busbar PLTGU Blok 2 Tambaklorok dioperasikan Splitting dan beda Subsistem. 2. Pengoperasian PLTGU Tambaklorok dioperasikan maksimal 5 unit dalam Subsistem Ungaran 1,2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
+          <t>Jangka Pendek : Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3448,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload di SUTT 150 kV Ungaran- Pudakpayung apabila trip 1 sirkit pada ruas tersebut. 2.Keandalan rendah dan fleksibiltas operasi berkurang</t>
+          <t>1. Terjadi Overload di SUTT 150 kV Ungaran- Pudakpayung apabila trip 1 sirkit pada ruas tersebut. 2. Keandalan rendah dan fleksibiltas operasi berkurang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS Ungaran-Pudakpayung total target sebesar503 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2.Pengaturan PLTGU Tambaklorok eksisting minimal 250 MW maksimal 950 MW</t>
+          <t>1. Sudah terpasang OLS Ungaran-Pudakpayung total target sebesar 503 MW (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW). 2. Pengaturan PLTGU Tambaklorok eksisting minimal 250 MW maksimal 950 MW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.RekonfigurasiBSBRU(Bukit Semarang Baru) -Tx. (Ungaran - Weleri). (RUPTL2025-2034, COD 2026). 2.RekonduktoringSUTT 150 kVUngaran-Pudakpayung menjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD2026). RekonduktoringSUTT 150 kVPandeanlamper- PudakpayungmenjadiHTLSC, 1250 Apersirkit(RUPTL 2025-2034, COD2026)</t>
+          <t>Jangka Pendek : 1.Rekonfigurasi BSBRU(Bukit Semarang Baru) -Tx. (Ungaran - Weleri). (RUPTL 2025-2034, COD 2026). 2.Rekonduktoring SUTT 150 kV Ungaran-Pudakpayung menjadi HTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2026). Rekonduktoring SUTT 150 kV Pandeanlamper- Pudakpayung menjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2026)</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3483,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload di SUTT 150 kV Pudakpayung- Pandeanlamper apabila trip 1 sirkit pada ruas tersebut. 2.Keandalan rendah dan fleksibiltas operasi berkurang</t>
+          <t>1. Terjadi Overload di SUTT 150 kV Pudakpayung- Pandeanlamper apabila trip 1 sirkit pada ruas tersebut. 2. Keandalan rendah dan fleksibiltas operasi berkurang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS Ungaran- Pudakpayungtotal targetsebesar503 MW(RealisasiBPTahun 2025, 14 Oktober 2025 -5721 MW). 2.Pengaturan PLTGU Tambaklorok eksisting minimal 250 MW maksimal 950 MW</t>
+          <t>1. Sudah terpasang OLS Ungaran- Pudakpayung total target sebesar503 MW(Realisasi BPTahun 2025, 14 Oktober 2025 - 5721 MW). 2. Pengaturan PLTGU Tambaklorok eksisting minimal 250 MW maksimal 950 MW</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.RekonfigurasiBSBRU(Bukit Semarang Baru) -Tx. (Ungaran - Weleri). (RUPTL2025-2034, COD 2026). 2.RekonduktoringSUTT 150 kVUngaran-Pudakpayung menjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD2026). 3.RekonduktoringSUTT 150 kVPandeanlamper- PudakpayungmenjadiHTLSC, 1250 Apersirkit(RUPTL 2025-2034, COD2026)</t>
+          <t>Jangka Pendek: 1. RekonfigurasiBSBRU(Bukit Semarang Baru) -Tx. (Ungaran - Weleri). (RUPTL 2025-2034, COD 2026). 2. RekonduktoringSUTT 150 kV Ungaran-Pudakpayung menjadi HTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2026). 3. RekonduktoringSUTT 150 kV Pandeanlamper- Pudakpayung menjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2026)</t>
         </is>
       </c>
     </row>
@@ -3851,17 +3518,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload di SKTT 150 kV Pandeanlamper- Simpanglima bila dioperasikan looping. 2.Berpotensi padam sebesar 79 MW bila terjadi gangguan N-2 di ruas penghantar SKTT 150 kV Pandeanlamper- Simpanglima- Kalisari. 3.Keandalan pusat kota Semarang (GIS Simpanglima) berkurang</t>
+          <t>1. Terjadi Overload di SKTT 150 kV Pandeanlamper- Simpanglima bila dioperasikan looping. 2. Berpotensi padam sebesar 79 MW bila terjadi gangguan N-2 di ruas penghantar SKTT 150 kV Pandeanlamper- Simpanglima- Kalisari. 3. Keandalan pusat kota Semarang (GIS Simpanglima) berkurang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.Pengoperasian radial GIS 150 kV Simpanglima melalui SKTT 150 kV Simpanglima- Pandeanlamper (GIS Simpang lima bay Kalisari open). 2.Pengaturan PLTGU Tambaklorok maksimal 200 MW pada saat looping di GIS Simpanglima saat ada manuver pekerjaan</t>
+          <t>1. Pengoperasian radial GIS 150 kV Simpanglima melalui SKTT 150 kV Simpanglima- Pandeanlamper (GIS Simpang lima bay Kalisari open). 2. Pengaturan PLTGU Tambaklorok maksimal 200 MW pada saat looping di GIS Simpanglima saat ada manuver pekerjaan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>JangkaPendek: Pembangunan SKTT 150 kV Pandeanlamper-Simpanglima sirkit CU 1200 A per sirkit (RUPTL2025-2034, COD 2028)</t>
+          <t>Jangka Pendek: Pembangunan SKTT 150 kV Pandeanlamper-Simpanglima sirkit CU 1200 A per sirkit (RUPTL 2025-2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -3886,17 +3553,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload di SKTT 150 kV Pandeanlamper- Simpanglima bila dioperasikan looping. 2.Berpotensi padam sebesar 79 MW bila terjadi gangguan N-2 di ruas penghantar SKTT 150 kV Pandeanlamper- Simpanglima- Kalisari. 3.Keandalan pusat kota Semarang (GIS Simpanglima) berkurang</t>
+          <t>1. Terjadi Overload di SKTT 150 kV Pandeanlamper- Simpanglima bila dioperasikan looping. 2. Berpotensi padam sebesar 79 MW bila terjadi gangguan N-2 di ruas penghantar SKTT 150 kV Pandeanlamper- Simpanglima- Kalisari. 3. Keandalan pusat kota Semarang (GIS Simpanglima) berkurang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.Pengoperasian radial GIS 150 kV Simpanglima melalui SKTT 150 kV Simpanglima- Pandeanlamper (GIS Simpang lima bay Kalisari open). 2.Pengaturan PLTGU Tambaklorok maksimal 200 MW pada saat looping di GIS Simpanglima saat ada manuver pekerjaan</t>
+          <t>1. Pengoperasian radial GIS 150 kV Simpanglima melalui SKTT 150 kV Simpanglima- Pandeanlamper (GIS Simpang lima bay Kalisari open). 2. Pengaturan PLTGU Tambaklorok maksimal 200 MW pada saat looping di GIS Simpanglima saat ada manuver pekerjaan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan SKTT 150 kV Simpanglima-Kalisari, 2 sirkit CU 1200 A per sirkit (RUPTL 2025-2034, COD 2028)</t>
+          <t>Jangka Pendek : Pembangunan SKTT 150 kV Simpanglima-Kalisari, 2 sirkit CU 1200 A per sirkit (RUPTL 2025-2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -3921,17 +3588,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload pada IBT Ungaran 1,2 saat gangguan PLTGU Tambaklorok B3. 2.Berpotensi padam beban sebesar 528 MW saat OLS IBT Ungaran bekerja. 3.Kesulitan dalam pemeliharaan pembangkit</t>
+          <t>1. Terjadi Overload pada IBT Ungaran 1,2 saat gangguan PLTGU Tambaklorok B3. 2. Berpotensi padam beban sebesar 528 MW saat OLS IBT Ungaran bekerja. 3. Kesulitan dalam pemeliharaan pembangkit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mengoperasikan minimal 2 unit PLTGU Tambaklorok eksisting sebagai backup saat PLTGUBlok 3 operasi maupunpekerjaan IBT Ungaran &amp; outletnya</t>
+          <t>Mengoperasikan minimal 2 unit PLTGU Tambaklorok eksisting sebagai backup saat PLTGU Blok 3 operasi maupun pekerjaan IBT Ungaran &amp; outletnya</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Rencana COD 2026. 2.RekonduktoringSUTT150 kVPandeanlamper- Tambaklorok menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028). 3.RekonduktoringSUTT150 kVTambaklorok-Ungaran menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028 Jangka Panjang: 4.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034,CODTahun2032</t>
+          <t>Jangka Pendek: 1. Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Rencana COD 2026. 2. RekonduktoringSUTT150 kV Pandeanlamper- Tambaklorok menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028). 3. RekonduktoringSUTT150 kV Tambaklorok-Ungaran menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028 Jangka Panjang : 4. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034, CODTahun2032</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3618,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] SUTT Tambaklorok - Pandeanlamper berbeban &gt;60% apabila PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[BELUM_DITETAPKAN] SUTT Tambaklorok - Pandeanlamper berbeban &gt; 60% apabila PLTGU Tambaklorokberoper asi total di atas 950 MW</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3966,7 +3633,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2.RekonduktoringSUTT150 kVPandeanlamper- Tambaklorok menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028 3.RekonduktoringSUTT150 kVTambaklorok-Ungaran menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028. Usulan / Solusi Jangka Menengah: 4.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
+          <t>Jangka Pendek : 1. Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2. RekonduktoringSUTT150 kV Pandeanlamper- Tambaklorok menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028 3. RekonduktoringSUTT150 kV Tambaklorok-Ungaran menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028. Usulan / Solusi Jangka Menengah : 4. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
         </is>
       </c>
     </row>
@@ -3986,22 +3653,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] GI Sayung dan SUTT 150 kV Tambaklorok- Sayung 1,2 dengan kondisi kritis karena berada pada tanah dengan kondisi penurunan tanah yang cukup tinggi sekitar ±5 cm perTahun dan dalam kondisi terendam sehingga pondasi dan struktur tower tidak dapat termonitor</t>
+          <t>[BELUM_DITETAPKAN] GI Sayung dan SUTT 150 kV Tambaklorok - Sayung 1,2 dengan kondisi kritis karena berada pada tanah dengan kondisi penurunan tanah yang cukup tinggi sekitar ±5 cm perTahun dan dalam kondisi terendam sehingga pondasi dan struktur tower tidak dapat termonitor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.Keandalan pasokan GI Sayung berkurang. 2.Pemulihan gangguan berpotensi terkendala karena SUTT Tambaklorok - Sayung 1,2 merupakan jalur pemulihan (Backfeed) Subsistem Tanjung Jati untuk pengiriman tegangan ke PLTU Rembang</t>
+          <t>1. Keandalan pasokan GI Sayung berkurang. 2. Pemulihan gangguan berpotensi terkendala karena SUTT Tambaklorok - Sayung 1,2 merupakan jalur pemulihan (Backfeed) Subsistem Tanjung Jati untuk pengiriman tegangan ke PLTU Rembang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.Pengaturan pembebananSUTT Tambaklorok - Sayung 1,2 (hanya memasok GI Sayung) denganposisi kopel Normally Open. Saat kondisi emergency, dilakukan pemindahan beban darisubsistem Ungaran ke subsistem Tanjungjati. 2.Monitoring tapak tower eksisting dan melaporkan kepada UP2B supaya tetap beroperasi sampai 2026 sebelum adanya rekonfigurasi ke SS Tanjung Jati</t>
+          <t>1. Pengaturan pembebanan SUTT Tambaklorok - Sayung 1,2 (hanya memasok GI Sayung) dengan posisi kopel Normally Open. Saat kondisi emergency, dilakukan pemindahan beban dari subsistem Ungaran ke subsistem Tanjungjati. 2. Monitoring tapak tower eksisting dan melaporkan kepada UP2B supaya tetap beroperasi sampai 2026 sebelum adanya rekonfigurasi ke SS Tanjung Jati</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025- 2034,COD 2026) informasi terupdate COD Desember 2027. 2.PercepatanpembangunanGI TETPurwodadibeserta outletnya (RUPTL 2025- 2034,COD2028). 3.Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung(RUPTL 2025-2034,COD 2028). 4.Usulan rerouting SUTT 150 kV Tambaklorok - Sayung 1,2, diusulkan COD 2028. Jangka Menengah: 5.Usulan baru pemindahan GI Sayung, diusulkan COD 2029</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025- 2034,COD 2026) informasi terupdate COD Desember 2027. 2.Percepatanpembangunan GI TET Purwodadi beserta outletnya (RUPTL 2025- 2034,COD 2028). 3. Pembangunan outlet GITET Purwodadi SUTT 150 kV Purwodadi-Sayung (RUPTL 2025-2034,COD 2028). 4. Usulan rerouting SUTT 150 kV Tambaklorok - Sayung 1,2, diusulkan COD 2028. Jangka Menengah : 5. Usulan baru pemindahan GI Sayung, diusulkan COD 2029</t>
         </is>
       </c>
     </row>
@@ -4021,22 +3688,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Pembebanan Trafo GI Kaliwungu dan GI Randugarut (memasok KTT KEK Kendal) telah berbeban &gt;90%. Daya konsumen KEK Kendal yang tersambung saat ini adalah 181,11 MVA dan pada akhir Tahun 2025 diproyeksikan sebesar 340,25 MVA sehingga kapasitas GI Kaliwungu sudah tidak mencukupi dan berpotensi juga terjadipenurunan tegangan</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan Trafo GI Kaliwungu dan GI Randugarut (memasok KTT KEK Kendal) telah berbeban &gt;90%. Daya konsumen KEK Kendal yang tersambung saat ini adalah 181,11 MVA dan pada akhir Tahun 2025 diproyeksikan sebesar 340,25 MVA sehingga kapasitas GI Kaliwungu sudah tidak mencukupi dan berpotensi juga terjadi penurunan tegangan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.Potensi Overload pada Trafo GI Kaliwungu dan GI Randugarut. 2.Potensi ekskursi tegangan pada GI Kaliwungu saat gangguan pada PLTGU Tambaklorok Blok 3 saat beban KEK Kendal sesuai proyeksi pada Tahun 2025</t>
+          <t>1. Potensi Overload pada Trafo GI Kaliwungu dan GI Randugarut. 2. Potensi ekskursi tegangan pada GI Kaliwungu saat gangguan pada PLTGU Tambaklorok Blok 3 saat beban KEK Kendal sesuai proyeksi pada Tahun 2025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2.Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
+          <t>1. Pengoperasian PLTGU Tambaklorok minimum 250 MW. 2. Memastikan pasokan Gas PLTGU Tambaklorok tercukupi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GI KEK Kendal, sesuai RUPTL 2025-2034 COD Tahun 2025. 2.Pembangunan Inc. GI KEK Kendal (SUTT Kaliwungu- Weleri) RUPTL 2025-2034 COD Tahun 2025. 3.Usulan baru pemasangan kapasitor 50 MVAR di GI KEK Kendal. Usulan COD Tahun 2026. 4.Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD Tahun 2028. (Menunggu kepastian KEK Kendal)</t>
+          <t>Jangka Pendek: 1. Pembangunan GI KEK Kendal, sesuai RUPTL 2025-2034 COD Tahun 2025. 2. Pembangunan Inc. GI KEK Kendal (SUTT Kaliwungu- Weleri) RUPTL 2025-2034 COD Tahun 2025. 3. Usulan baru pemasangan kapasitor 50 MVAR di GI KEK Kendal. Usulan COD Tahun 2026. 4. Pembangunan GITET Weleri, sesuai RUPTL 2025-2034 COD Tahun 2028. (Menunggu kepastian KEK Kendal)</t>
         </is>
       </c>
     </row>
@@ -4056,7 +3723,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1-1] SUTT Tambaklorok - Krapyak akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KLSRI, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[N-1-1] SUTT Tambaklorok - Krapyak akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KLSRI, serta saat PLTGU Tambaklorokberoper asi total di atas 950 MW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4071,7 +3738,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2. RekonduktoringSUTT150 kVPandeanlamper- Tambaklorok menjadiHTLSC, 2400A Usulan / Solusi persirkit(RUPTL2025- 2034, COD 2028). 3. RekonduktoringSUTT150 kVTambaklorok-Ungaran menjadiHTLSC, 2400A persirkit(RUPTL2025- 2034, COD 2028. Jangka Panjang: 4. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
+          <t>Jangka Pendek: 1. Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2. Rekonduktoring SUTT150 kV Pandeanlamper- Tambaklorok menjadi HTLSC, 2400A Usulan / Solusi per sirkit(RUPTL2025- 2034, COD 2028). 3. Rekonduktoring SUTT150 kV Tambaklorok-Ungaran menjadi HTLSC, 2400A per sirkit(RUPTL2025- 2034, COD 2028. Jangka Panjang: 4. Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
         </is>
       </c>
     </row>
@@ -4091,7 +3758,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[N-1-1] SUTT Tambaklorok - Kalisari akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KRAPK, serta saat PLTGU Tambaklorokberoper asi total di atas950 MW</t>
+          <t>[N-1-1] SUTT Tambaklorok - Kalisari akan mengalami overload apabila terjadi kontingensi N-2 SUTT TBROK-PDLAM, N-1-1 TBROK-PDLAM &amp; TBROK-KRAPK, serta saat PLTGU Tambaklorokberoper asi total di atas 950 MW</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4106,7 +3773,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rencana PemasanganDS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2.RekonduktoringSUTT150 kVPandeanlamper- Tambaklorok menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028). 3.RekonduktoringSUTT150 kVTambaklorok-Ungaran menjadiHTLSC, 2400A persirkit(RUPTL2025-2034, COD 2028. Jangka Panjang: 4.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
+          <t>Jangka Pendek: 1. Rencana Pemasangan DS OGS pada outlet PLTGU Tambaklorok Tambaklorok Rencana COD 2026. 2. RekonduktoringSUTT150 kV Pandeanlamper- Tambaklorok menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028). 3. RekonduktoringSUTT150 kV Tambaklorok-Ungaran menjadi HTLSC, 2400A per sirkit(RUPTL2025-2034, COD 2028. Jangka Panjang: 4.Pembangunan GITET Tambaklorok, sesuai RUPTL 2025-2034 COD Tahun 2032</t>
         </is>
       </c>
     </row>
